--- a/06-normatividad/checklist-cliente.xlsx
+++ b/06-normatividad/checklist-cliente.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="1" r:id="R7ad721dfa7e6465e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="1" r:id="R9ddb891a4c634724"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,9 +13,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="2">
+  <x:numFmts count="3">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="dd/mm/yyyy"/>
+    <x:numFmt numFmtId="202" formatCode="General"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -142,7 +143,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="30">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -228,6 +229,9 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -240,7 +244,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF4CCCC"/>
         </x:patternFill>
       </x:fill>
@@ -251,7 +255,7 @@
         <x:color rgb="FF9C5700"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE5CD"/>
         </x:patternFill>
       </x:fill>
@@ -262,7 +266,7 @@
         <x:color rgb="FF7F6000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -273,7 +277,7 @@
         <x:color rgb="FF7F6000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -284,7 +288,7 @@
         <x:color rgb="FF274E13"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAD3"/>
         </x:patternFill>
       </x:fill>
@@ -295,7 +299,7 @@
         <x:color rgb="FF274E13"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAD3"/>
         </x:patternFill>
       </x:fill>
@@ -305,7 +309,7 @@
         <x:color rgb="FF666666"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF2F2F2"/>
         </x:patternFill>
       </x:fill>
@@ -316,7 +320,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF4CCCC"/>
         </x:patternFill>
       </x:fill>
@@ -327,7 +331,7 @@
         <x:color rgb="FF9C5700"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE5CD"/>
         </x:patternFill>
       </x:fill>
@@ -338,7 +342,7 @@
         <x:color rgb="FF7F6000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -349,7 +353,7 @@
         <x:color rgb="FF274E13"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAD3"/>
         </x:patternFill>
       </x:fill>
@@ -372,7 +376,7 @@
     <x:tableColumn id="8" name="Brecha"/>
     <x:tableColumn id="9" name="Acción"/>
     <x:tableColumn id="10" name="Responsable"/>
-    <x:tableColumn id="11" name="Fecha objetivo"/>
+    <x:tableColumn id="11" name="Hito objetivo propuesto"/>
     <x:tableColumn id="12" name="Prioridad"/>
     <x:tableColumn id="13" name="Observaciones"/>
   </x:tableColumns>
@@ -588,7 +592,7 @@
     <x:col min="8" max="8" width="40" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="38" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="25" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="25" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="13" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="32" hidden="0" customWidth="1"/>
   </x:cols>
@@ -627,7 +631,7 @@
     </x:row>
     <x:row r="3" ht="34" customHeight="1">
       <x:c r="A3" s="8" t="str">
-        <x:v>Evaluación preliminar para el Directorio de extensiones. No constituye concepto jurídico. La base legal, retención, políticas internas y roles deben validarse con Jurídica, Privacidad, Seguridad y Tecnología.</x:v>
+        <x:v>Evaluación preliminar; no es concepto jurídico. Políticas, base jurídica, permisos y retención por validar. Hitos propuestos, no fechas acordadas; cada responsable debe confirmarlos.</x:v>
       </x:c>
       <x:c r="B3" s="8"/>
       <x:c r="C3" s="8"/>
@@ -754,7 +758,7 @@
         <x:v>Responsable</x:v>
       </x:c>
       <x:c r="K8" s="21" t="str">
-        <x:v>Fecha objetivo</x:v>
+        <x:v>Hito objetivo propuesto</x:v>
       </x:c>
       <x:c r="L8" s="21" t="str">
         <x:v>Prioridad</x:v>
@@ -794,7 +798,9 @@
       <x:c r="J9" s="24" t="str">
         <x:v>Dueña del proceso / Jurídica</x:v>
       </x:c>
-      <x:c r="K9" s="26"/>
+      <x:c r="K9" s="30" t="str">
+        <x:v>Antes de usar datos reales</x:v>
+      </x:c>
       <x:c r="L9" s="25" t="str">
         <x:v>Alta</x:v>
       </x:c>
@@ -833,7 +839,9 @@
       <x:c r="J10" s="24" t="str">
         <x:v>Jurídica / Privacidad</x:v>
       </x:c>
-      <x:c r="K10" s="26"/>
+      <x:c r="K10" s="30" t="str">
+        <x:v>Antes de usar datos reales</x:v>
+      </x:c>
       <x:c r="L10" s="25" t="str">
         <x:v>Crítica</x:v>
       </x:c>
@@ -872,7 +880,9 @@
       <x:c r="J11" s="24" t="str">
         <x:v>Jurídica / Comunicaciones</x:v>
       </x:c>
-      <x:c r="K11" s="26"/>
+      <x:c r="K11" s="30" t="str">
+        <x:v>Antes del piloto</x:v>
+      </x:c>
       <x:c r="L11" s="25" t="str">
         <x:v>Alta</x:v>
       </x:c>
@@ -911,7 +921,9 @@
       <x:c r="J12" s="24" t="str">
         <x:v>Arquitectura / Privacidad</x:v>
       </x:c>
-      <x:c r="K12" s="26"/>
+      <x:c r="K12" s="30" t="str">
+        <x:v>Antes del piloto</x:v>
+      </x:c>
       <x:c r="L12" s="25" t="str">
         <x:v>Alta</x:v>
       </x:c>
@@ -950,7 +962,9 @@
       <x:c r="J13" s="24" t="str">
         <x:v>Gestora del proceso</x:v>
       </x:c>
-      <x:c r="K13" s="26"/>
+      <x:c r="K13" s="30" t="str">
+        <x:v>En el piloto y cada corte</x:v>
+      </x:c>
       <x:c r="L13" s="25" t="str">
         <x:v>Alta</x:v>
       </x:c>
@@ -989,7 +1003,9 @@
       <x:c r="J14" s="24" t="str">
         <x:v>TI SharePoint / Seguridad</x:v>
       </x:c>
-      <x:c r="K14" s="26"/>
+      <x:c r="K14" s="30" t="str">
+        <x:v>Antes de usar datos reales</x:v>
+      </x:c>
       <x:c r="L14" s="25" t="str">
         <x:v>Crítica</x:v>
       </x:c>
@@ -1028,7 +1044,9 @@
       <x:c r="J15" s="24" t="str">
         <x:v>Seguridad / TI</x:v>
       </x:c>
-      <x:c r="K15" s="26"/>
+      <x:c r="K15" s="30" t="str">
+        <x:v>Antes del piloto</x:v>
+      </x:c>
       <x:c r="L15" s="25" t="str">
         <x:v>Crítica</x:v>
       </x:c>
@@ -1067,7 +1085,9 @@
       <x:c r="J16" s="24" t="str">
         <x:v>Líder del proyecto / Cliente</x:v>
       </x:c>
-      <x:c r="K16" s="26"/>
+      <x:c r="K16" s="30" t="str">
+        <x:v>Antes de compartir evidencias</x:v>
+      </x:c>
       <x:c r="L16" s="25" t="str">
         <x:v>Alta</x:v>
       </x:c>
@@ -1106,7 +1126,9 @@
       <x:c r="J17" s="24" t="str">
         <x:v>Jurídica / Privacidad</x:v>
       </x:c>
-      <x:c r="K17" s="26"/>
+      <x:c r="K17" s="30" t="str">
+        <x:v>Antes de usar datos reales</x:v>
+      </x:c>
       <x:c r="L17" s="25" t="str">
         <x:v>Crítica</x:v>
       </x:c>
@@ -1145,7 +1167,9 @@
       <x:c r="J18" s="24" t="str">
         <x:v>Privacidad / Servicio al empleado</x:v>
       </x:c>
-      <x:c r="K18" s="26"/>
+      <x:c r="K18" s="30" t="str">
+        <x:v>Antes del piloto</x:v>
+      </x:c>
       <x:c r="L18" s="25" t="str">
         <x:v>Alta</x:v>
       </x:c>
@@ -1184,7 +1208,9 @@
       <x:c r="J19" s="24" t="str">
         <x:v>Archivo / Jurídica / TI</x:v>
       </x:c>
-      <x:c r="K19" s="26"/>
+      <x:c r="K19" s="30" t="str">
+        <x:v>Antes de usar datos reales</x:v>
+      </x:c>
       <x:c r="L19" s="25" t="str">
         <x:v>Crítica</x:v>
       </x:c>
@@ -1223,7 +1249,9 @@
       <x:c r="J20" s="24" t="str">
         <x:v>Seguridad / Privacidad</x:v>
       </x:c>
-      <x:c r="K20" s="26"/>
+      <x:c r="K20" s="30" t="str">
+        <x:v>Antes del piloto</x:v>
+      </x:c>
       <x:c r="L20" s="25" t="str">
         <x:v>Crítica</x:v>
       </x:c>
@@ -1262,7 +1290,9 @@
       <x:c r="J21" s="24" t="str">
         <x:v>Seguridad / TI</x:v>
       </x:c>
-      <x:c r="K21" s="26"/>
+      <x:c r="K21" s="30" t="str">
+        <x:v>Antes del piloto; luego periódica</x:v>
+      </x:c>
       <x:c r="L21" s="25" t="str">
         <x:v>Alta</x:v>
       </x:c>
@@ -1301,7 +1331,9 @@
       <x:c r="J22" s="24" t="str">
         <x:v>Dueña del proceso / Privacidad</x:v>
       </x:c>
-      <x:c r="K22" s="26"/>
+      <x:c r="K22" s="30" t="str">
+        <x:v>Antes del piloto y cada revisión</x:v>
+      </x:c>
       <x:c r="L22" s="25" t="str">
         <x:v>Alta</x:v>
       </x:c>
@@ -1340,7 +1372,9 @@
       <x:c r="J23" s="24" t="str">
         <x:v>Jurídica / Compras / TI</x:v>
       </x:c>
-      <x:c r="K23" s="26"/>
+      <x:c r="K23" s="30" t="str">
+        <x:v>Antes del despliegue</x:v>
+      </x:c>
       <x:c r="L23" s="25" t="str">
         <x:v>Alta</x:v>
       </x:c>
@@ -1379,7 +1413,9 @@
       <x:c r="J24" s="24" t="str">
         <x:v>Equipo del proyecto</x:v>
       </x:c>
-      <x:c r="K24" s="26"/>
+      <x:c r="K24" s="30" t="str">
+        <x:v>Antes de cada prueba o demo</x:v>
+      </x:c>
       <x:c r="L24" s="25" t="str">
         <x:v>Alta</x:v>
       </x:c>
@@ -1387,7 +1423,7 @@
         <x:v>Anonimizar también metadatos y nombres de archivos.</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="64" customHeight="1">
+    <x:row r="25" ht="104" customHeight="1">
       <x:c r="A25" s="24" t="str">
         <x:v>REPO-01</x:v>
       </x:c>
@@ -1404,26 +1440,28 @@
         <x:v>Repositorio limitado a documentación, diagramas y ejemplos ficticios.</x:v>
       </x:c>
       <x:c r="F25" s="24" t="str">
-        <x:v>Revisión de archivos e historial antes de entrega.</x:v>
+        <x:v>README, .gitignore y revisión del árbol de archivos de esta entrega antes del commit.</x:v>
       </x:c>
       <x:c r="G25" s="25" t="str">
         <x:v>Cumple</x:v>
       </x:c>
       <x:c r="H25" s="24" t="str">
-        <x:v>No se observaron datos reales en los artefactos revisados.</x:v>
+        <x:v>No se observaron nóminas ni directorio operativo en los archivos revisados. Esto no certifica todo el historial.</x:v>
       </x:c>
       <x:c r="I25" s="24" t="str">
-        <x:v>Mantener revisión final y reglas de exclusión.</x:v>
+        <x:v>Revisar cada publicación; excluir datos reales y verificar que no estén ya versionados.</x:v>
       </x:c>
       <x:c r="J25" s="24" t="str">
         <x:v>Equipo del proyecto</x:v>
       </x:c>
-      <x:c r="K25" s="26"/>
+      <x:c r="K25" s="30" t="str">
+        <x:v>Antes de cada publicación</x:v>
+      </x:c>
       <x:c r="L25" s="25" t="str">
         <x:v>Alta</x:v>
       </x:c>
       <x:c r="M25" s="24" t="str">
-        <x:v>El estado debe reevaluarse si se agregan capturas.</x:v>
+        <x:v>Cumple limitado al árbol revisado el 02/10/2026. No implica cumplimiento integral; reevaluar capturas y metadatos. Créditos académicos no son nómina.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="64" customHeight="1">
@@ -1457,7 +1495,9 @@
       <x:c r="J26" s="24" t="str">
         <x:v>Líder del proyecto / Cliente</x:v>
       </x:c>
-      <x:c r="K26" s="26"/>
+      <x:c r="K26" s="30" t="str">
+        <x:v>Al cierre del proyecto</x:v>
+      </x:c>
       <x:c r="L26" s="25" t="str">
         <x:v>Alta</x:v>
       </x:c>
@@ -2008,7 +2048,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51e09a9ce2b14cf9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra7486b58787e4cfb"/>
   </x:tableParts>
 </x:worksheet>
 </file>